--- a/Data/ItemDef.xlsx
+++ b/Data/ItemDef.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13290" windowHeight="4485"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
   <si>
     <t>道具定义表</t>
   </si>
@@ -71,7 +71,22 @@
     <t>堆叠上限</t>
   </si>
   <si>
+    <t>资源1</t>
+  </si>
+  <si>
     <t>Resource</t>
+  </si>
+  <si>
+    <t>资源2</t>
+  </si>
+  <si>
+    <t>资源3</t>
+  </si>
+  <si>
+    <t>资源4</t>
+  </si>
+  <si>
+    <t>资源5</t>
   </si>
   <si>
     <t>Tool</t>
@@ -1062,13 +1077,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="15.875" customWidth="1"/>
     <col min="2" max="2" width="22.25" customWidth="1"/>
     <col min="3" max="3" width="24.5" customWidth="1"/>
     <col min="4" max="4" width="25.5" customWidth="1"/>
+    <col min="5" max="5" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1131,8 +1147,14 @@
       <c r="A5" s="1">
         <v>100000</v>
       </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5">
         <v>9999</v>
@@ -1140,56 +1162,112 @@
     </row>
     <row r="6" ht="15.75" spans="1:5">
       <c r="A6" s="1">
-        <v>200000</v>
-      </c>
-      <c r="D6" s="1" t="s">
+        <v>100001</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
         <v>15</v>
-      </c>
-      <c r="E6">
-        <v>9999</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:5">
       <c r="A7" s="1">
-        <v>300000</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7">
-        <v>9999</v>
+        <v>100002</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:5">
       <c r="A8" s="1">
-        <v>400000</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8">
-        <v>9999</v>
+        <v>100003</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:5">
       <c r="A9" s="1">
-        <v>500000</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9">
-        <v>9999</v>
+        <v>100004</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:5">
       <c r="A10" s="1">
+        <v>200000</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" spans="1:5">
+      <c r="A11" s="1">
+        <v>300000</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" spans="1:5">
+      <c r="A12" s="1">
+        <v>400000</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" spans="1:5">
+      <c r="A13" s="1">
+        <v>500000</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" spans="1:5">
+      <c r="A14" s="1">
         <v>600000</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10">
+      <c r="D14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14">
         <v>9999</v>
       </c>
     </row>
